--- a/ig/DM-MARS-2026/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="2193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3268" uniqueCount="2191">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V102</t>
+    <t>V103</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T00:00:00+00:00</t>
+    <t>2026-04-13T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1047</t>
+    <t>1046</t>
   </si>
   <si>
     <t>Code</t>
@@ -1769,7 +1769,7 @@
     <t>4004</t>
   </si>
   <si>
-    <t>DPN : TRISOMIE 21 FOETALE : DEPISTAGE 2E TRIMESTRE, MARQUEURS SERIQUES MATERNELS</t>
+    <t>DPN:TRISOMIE 21 FOETALE : DEPISTAGE 2E TRIMESTRE,MARQUEURS SERIQUES MATERNELS</t>
   </si>
   <si>
     <t>1704</t>
@@ -1937,7 +1937,7 @@
     <t>4046</t>
   </si>
   <si>
-    <t>DPN PROPREMENT DIT  : MUCOVISCIDOSE : POLYMORPHISME DE L'ADN</t>
+    <t>DPN PROPREMENT DIT : MUCOVISCIDOSE : POLYMORPHISME DE L'ADN</t>
   </si>
   <si>
     <t>1415</t>
@@ -4013,12 +4013,6 @@
     <t>FACTEUR V (PROACCELERINE)- DOSAGE ACTIVITE COAGULANTE</t>
   </si>
   <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>VITESSE DE SEDIMENTATION (VS)</t>
-  </si>
-  <si>
     <t>1257</t>
   </si>
   <si>
@@ -5081,7 +5075,7 @@
     <t>4058</t>
   </si>
   <si>
-    <t>DPN : ALPHA-THALASSEMIE AVEC ANTECEDENTS FAMILIAUX CONNUS</t>
+    <t>DPN:ALPHA-THALASSEMIE AVEC ANTECEDENTS FAMILIAUX CONNUS</t>
   </si>
   <si>
     <t>1318</t>
@@ -6398,7 +6392,7 @@
     <t>4095</t>
   </si>
   <si>
-    <t>DPN : DEFICIT CONGENITAL EN FACTEUR DE L'HEMOSTASE (VIII , IX , W, PROT C, S..)</t>
+    <t>DPN:DEFICIT CONGENITAL EN FACTEUR DE L'HEMOSTASE(VIII , IX , W, PROT C, S..)</t>
   </si>
   <si>
     <t>0332</t>
@@ -7234,7 +7228,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1048"/>
+  <dimension ref="A1:D1047"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -15169,7 +15163,7 @@
         <v>1415</v>
       </c>
       <c r="C660" t="s" s="2">
-        <v>1416</v>
+        <v>260</v>
       </c>
       <c r="D660" s="2"/>
     </row>
@@ -15178,10 +15172,10 @@
         <v>95</v>
       </c>
       <c r="B661" t="s" s="2">
+        <v>1416</v>
+      </c>
+      <c r="C661" t="s" s="2">
         <v>1417</v>
-      </c>
-      <c r="C661" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="D661" s="2"/>
     </row>
@@ -19167,21 +19161,21 @@
       <c r="C993" t="s" s="2">
         <v>2081</v>
       </c>
-      <c r="D993" s="2"/>
+      <c r="D993" t="s" s="2">
+        <v>2082</v>
+      </c>
     </row>
     <row r="994">
       <c r="A994" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B994" t="s" s="2">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="C994" t="s" s="2">
-        <v>2083</v>
-      </c>
-      <c r="D994" t="s" s="2">
         <v>2084</v>
       </c>
+      <c r="D994" s="2"/>
     </row>
     <row r="995">
       <c r="A995" t="s" s="2">
@@ -19263,7 +19257,7 @@
         <v>2097</v>
       </c>
       <c r="C1001" t="s" s="2">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="D1001" s="2"/>
     </row>
@@ -19272,7 +19266,7 @@
         <v>95</v>
       </c>
       <c r="B1002" t="s" s="2">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="C1002" t="s" s="2">
         <v>2099</v>
@@ -19313,21 +19307,21 @@
       <c r="C1005" t="s" s="2">
         <v>2105</v>
       </c>
-      <c r="D1005" s="2"/>
+      <c r="D1005" t="s" s="2">
+        <v>2106</v>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B1006" t="s" s="2">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="C1006" t="s" s="2">
-        <v>2107</v>
-      </c>
-      <c r="D1006" t="s" s="2">
         <v>2108</v>
       </c>
+      <c r="D1006" s="2"/>
     </row>
     <row r="1007">
       <c r="A1007" t="s" s="2">
@@ -19820,18 +19814,6 @@
         <v>2190</v>
       </c>
       <c r="D1047" s="2"/>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B1048" t="s" s="2">
-        <v>2191</v>
-      </c>
-      <c r="C1048" t="s" s="2">
-        <v>2192</v>
-      </c>
-      <c r="D1048" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
